--- a/登录测试用例_最终.xlsx
+++ b/登录测试用例_最终.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>用户名首尾空格</t>
+          <t>用户名首尾空格自动去除后登录</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>停留在登录页并显示错误提示</t>
+          <t>登录成功并离开登录页</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
